--- a/human_validation/judge/kor/judge_D021_S003_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S003_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 저희 병원 담당 선생님이 좀 밀어붙이셔서 오게 됐어요. 제가 어떻게 먹는지에 대해 계속 말씀하셨거든요. 대부분 날에는 그냥 간단하게 해요. 아침에 커피 마시고, 일하는 중간에 몇 입 정도 먹고, 수업 과제로 너무 바쁘지 않으면 저녁을 조금 먹어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 더 먹고 싶은데 뭔가가 막는 느낌인가요, 아니면 대부분 그냥 먹고 싶은 생각이 안 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 더 먹고 싶은데 저 스스로 막는다는 건 잘 모르겠어요. 대부분 날에는 그냥 기본적으로 해요. 아침에 커피 마시고, 일하는 중간에 몇 입 먹고, 수업 과제에 안 쫓기면 나중에 저녁을 조금 먹어요. 그냥 그 정도면 충분한 느낌이에요, 그런 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 최근에 체중이 줄으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네, 좀 그런 것 같아요. 작업복 바지가 예전보다 확실히 헐렁해졌고, 현장 사람들이 너무 말랐다고 했어요. 근데 저는 그렇게는 안 보여요. 그냥 하루 종일 서서 일해서 살이 빠진 거라고 생각했거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 체중이 늘까 봐 걱정되시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네... 그러니까, 이런 식으로 말하는 게 좀 그런데, 맞아요. 피자나 큰 샌드위치처럼 정말 무거운 걸 먹으면, 다음 날 일어났을 때 더 커지거나 굼떠질 것 같은 불안한 느낌이 들어요. 일할 때 필요한 만큼 사다리나 방을 돌아다닐 수 없을 것 같은 느낌이요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 뭘 먹을지, 얼마나 먹을지 결정할 때 체중이나 몸매를 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 그래요. 그게 저를 더 커 보이거나 무겁게 느끼게 할지 생각해요. 피자나 큰 샌드위치 같은 거면, 일어났을 때 더 커지고 느려진 느낌이 들까 봐 불안해지고, 그럼 사다리를 돌아다니거나 필요한 만큼 일을 못 할 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 불편할 정도로 배가 부를 때까지 드신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 딱히 없어요. 그러니까, 보통 그 지경까지 가기 전에 멈춰요. 너무 배부른 느낌을 싫어해서 그러지 않으려고 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022) | 배제됨: 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 많이 먹기 시작하면 멈출 수 없을까 봐 걱정되시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 그게 저한테 진짜 문제는 아닌 것 같아요. 보통 너무 많이 안 먹으려고 하는 편이라, 멈출 수 없다는 느낌은 딱히 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 원하는 만큼 먹도록 자신에게 허락한다면 통제력을 잃을 것 같다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 저 스스로 그렇게 많이 먹도록 허락하지 않아서, 그러면 어떻게 될지는 모르겠어요. 완전히 통제력을 잃을 거라고 생각하기보다는, 그냥 그 지경까지 안 가려고 하는 거예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 체중이 조금 더 나간다면 더 행복할 거라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 아니요, 딱히 그렇지 않아요. 체중이 더 나간다는 생각 자체가 불안하게 만들어요. 피자나 큰 샌드위치처럼 무거운 걸 먹으면, 다음 날 일어났을 때 더 커지거나 굼떠질 것 같은 생각이 들기 시작하고, 그럼 일할 때 필요한 만큼 사다리나 방을 돌아다닐 수 없을 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 일단 먹기 시작하면 양을 조절하지 못할까 봐 걱정돼서 먹는 것에 불안을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 그게 저한테 주된 불안은 아닌 것 같아요. 먹기 시작하면서 멈추지 못할까 봐 걱정하는 건 아니에요. 그보다는 먹기 전에 조심하는 편이고, 불편해지는 지경까지 안 가게 하려고 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 본인의 식습관이 먹는 양에 대한 통제력을 잃는 것에 대한 두려움에 의해 좌우된다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 정확히는 그렇지 않은 것 같아요. 먹기 시작하면 통제력을 잃을까 봐 두렵다는 느낌은 딱히 없어요. 그보다는 모든 걸 적당히 조절하려 하고, 불편해지지 않게 하려는 거예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 본인의 식습관이 특정 체중이나 몸매를 유지하는 것을 목표로 한다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네, 그런 것 같아요. 더 무거워지지 않으려고 해요. 피자나 큰 샌드위치 같은 걸 먹으면, 다음 날 더 커지고 느려질 것 같은 불안한 느낌이 들고, 그럼 사다리나 좁은 방을 필요한 만큼 돌아다닐 수 없을 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 지난 몇 달 동안 체중이 상당히 많이 줄으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 네, 그러니까... 작업복 바지가 예전보다 확실히 헐렁해요. 요즘은 그냥 헐렁하게 걸쳐 있어요. 현장 사람들이 너무 말랐다고 하는데, 저는 그냥 하루 종일 서서 일해서 살이 빠진 거라고 보는 편이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 체중이 늘 것에 대한 두려움이 직장 밖의 일상 활동이나 인간관계에 영향을 주나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 네, 어느 정도는요. 여전히 일이랑 수업은 나가고 있어서, 모든 걸 그만둔 건 아니에요. 근데 동료들이랑 점심을 먹거나 스터디 모임에 가는 건 피하기 시작했어요, 제 루틴을 지키고 사람들이 제가 뭘 먹는지 보거나 뭐라고 하는 걸 안 겪는 게 더 편하거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 특정공포증 (D012); 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 본인이 너무 말랐다고 생각하시나요, 아니면 여전히 정상 체중이라고 보시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 다른 사람들처럼 무슨 응급 상황이라고는 딱히 안 보여요. 사람들이 저더러 너무 말랐다고 하는 건 아는데, 저한테는 그냥 절제하고 바쁘게 지내는 느낌이지, 제 체중에 심각하게 잘못된 게 있는 것 같지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 특정공포증 (D012) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 칼로리 섭취를 제한하려고 의식적으로 노력하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 네... 어떤 면에서는 그런 것 같아요. 제가 너무 적게 먹는다고 병원 선생님이 계속 말씀하셔서 여기 오게 됐어요. 대부분 날에는 그냥 간단하게 해요. 아침에 커피 마시고, 일하는 중간에 몇 입 먹고, 수업 과제에 너무 매여 있지 않으면 저녁을 조금 먹어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 특정공포증 (D012) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 먹는 것을 제한하는 주된 목표가 체중이 늘지 않게 하려는 건가요, 아니면 특정 몸매를 만들려는 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 대부분 체중이 늘지 않게 하려는 것 같아요. 그러니까, 피자나 큰 샌드위치처럼 무거운 걸 먹으면, 다음 날 더 커지고 느려질 것 같은 불안한 느낌이 들어요. 그리고 일할 때 필요한 만큼 사다리나 방을 돌아다닐 수 없을까 봐 걱정돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 특정공포증 (D012) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 피자나 큰 샌드위치 같은 무거운 식사를 피하는 목표가 주로 체중이 느는 게 두려워서인가요, 아니면 일을 위해 특정 몸매를 유지하고 싶어서인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 솔직히 체중이 느는 게 두려운 쪽에 더 가까워요. 일을 위한 특정 몸매를 딱히 생각하고 있는 건 아니에요. 무거운 걸 먹으면, 다음 날 더 커지고 무거워질까 봐 불안해지고, 그럼 사다리나 방을 필요한 만큼 돌아다닐 수 없을 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 특정공포증 (D012) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 다른 사람들이 너무 말랐다고 말할 때도, 본인이 너무 말랐다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 그러니까, 딱히 그렇지는 않아요. 사람들이 저더러 너무 말랐다고 하는 건 아는데, 그들처럼 무슨 응급 상황이라고는 안 봐요. 저한테는 그냥 별일 아닌 걸 크게 만드는 것처럼 느껴져요, 저는 그냥 절제하고 바쁜 것뿐인데요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 특정공포증 (D012) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 덜 먹는 목표가 특정 몸매를 만들기 위한 건가요, 아니면 그냥 체중이 늘지 않게 하려는 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 체중이 늘지 않게 하려는 쪽에 더 가까워요. 특정 몸매를 만들려는 건 아니에요. 그냥 피자나 큰 샌드위치처럼 무거운 걸 먹으면, 다음 날 더 커지고 느려질까 봐 정말 불안해지고, 그럼 일할 때 필요한 만큼 움직일 수 없을 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 신경성 식욕부진증 (D021)
 인구통계: 성별 여성 / 나이 33 / 직업상태 painter or paperhanger / 최종학력 대학 재학
@@ -575,488 +999,35 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S043
-배경 서술: 토냐가 리드 페인터 자격증과 소규모 사업 계획을 위한 야간 강의를 듣기 시작하면서, 안 그래도 현장 업무와 견적, 수습생 멘토링으로 꽉 찼던 하루가 더 빡빡하고 시간에 쫓기게 되었다. 그녀는 긴 근무일 동안 효율적이고 저렴하며 통제 가능하다고 느껴지는 것을 중심으로 식사를 짜기 시작했고, 시간이 지나면서 이 절식은 그녀의 체중을 건강 수준보다 상당히 낮출 정도로 지속되었다. 고객과 동료들이 그녀가 눈에 띄게 마른 것을 알아챘는데도, 토냐는 이를 현장 체력과 깨끗한 생활 습관 덕분이라고 설명했고, 체중이 늘면 몸이 느려질 것 같다는 강한 두려움을 계속 느꼈으며, 자신의 저체중을 의학적으로 심각한 문제로 여기지 않았다. 자격증 서류를 검토하던 산업보건 임상의가 그녀의 저체중을 발견하고 섭식장애 평가를 의뢰하면서, 그녀는 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 저희 병원 담당 선생님이 좀 밀어붙이셔서 오게 됐어요. 제가 어떻게 먹는지에 대해 계속 말씀하셨거든요. 대부분 날에는 그냥 간단하게 해요. 아침에 커피 마시고, 일하는 중간에 몇 입 정도 먹고, 수업 과제로 너무 바쁘지 않으면 저녁을 조금 먹어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 더 먹고 싶은데 뭔가가 막는 느낌인가요, 아니면 대부분 그냥 먹고 싶은 생각이 안 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 더 먹고 싶은데 저 스스로 막는다는 건 잘 모르겠어요. 대부분 날에는 그냥 기본적으로 해요. 아침에 커피 마시고, 일하는 중간에 몇 입 먹고, 수업 과제에 안 쫓기면 나중에 저녁을 조금 먹어요. 그냥 그 정도면 충분한 느낌이에요, 그런 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 최근에 체중이 줄으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네, 좀 그런 것 같아요. 작업복 바지가 예전보다 확실히 헐렁해졌고, 현장 사람들이 너무 말랐다고 했어요. 근데 저는 그렇게는 안 보여요. 그냥 하루 종일 서서 일해서 살이 빠진 거라고 생각했거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 체중이 늘까 봐 걱정되시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네... 그러니까, 이런 식으로 말하는 게 좀 그런데, 맞아요. 피자나 큰 샌드위치처럼 정말 무거운 걸 먹으면, 다음 날 일어났을 때 더 커지거나 굼떠질 것 같은 불안한 느낌이 들어요. 일할 때 필요한 만큼 사다리나 방을 돌아다닐 수 없을 것 같은 느낌이요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 뭘 먹을지, 얼마나 먹을지 결정할 때 체중이나 몸매를 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 그래요. 그게 저를 더 커 보이거나 무겁게 느끼게 할지 생각해요. 피자나 큰 샌드위치 같은 거면, 일어났을 때 더 커지고 느려진 느낌이 들까 봐 불안해지고, 그럼 사다리를 돌아다니거나 필요한 만큼 일을 못 할 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 불편할 정도로 배가 부를 때까지 드신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 딱히 없어요. 그러니까, 보통 그 지경까지 가기 전에 멈춰요. 너무 배부른 느낌을 싫어해서 그러지 않으려고 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022) | 배제됨: 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 많이 먹기 시작하면 멈출 수 없을까 봐 걱정되시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 그게 저한테 진짜 문제는 아닌 것 같아요. 보통 너무 많이 안 먹으려고 하는 편이라, 멈출 수 없다는 느낌은 딱히 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 원하는 만큼 먹도록 자신에게 허락한다면 통제력을 잃을 것 같다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 저 스스로 그렇게 많이 먹도록 허락하지 않아서, 그러면 어떻게 될지는 모르겠어요. 완전히 통제력을 잃을 거라고 생각하기보다는, 그냥 그 지경까지 안 가려고 하는 거예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 체중이 조금 더 나간다면 더 행복할 거라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 아니요, 딱히 그렇지 않아요. 체중이 더 나간다는 생각 자체가 불안하게 만들어요. 피자나 큰 샌드위치처럼 무거운 걸 먹으면, 다음 날 일어났을 때 더 커지거나 굼떠질 것 같은 생각이 들기 시작하고, 그럼 일할 때 필요한 만큼 사다리나 방을 돌아다닐 수 없을 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 일단 먹기 시작하면 양을 조절하지 못할까 봐 걱정돼서 먹는 것에 불안을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 그게 저한테 주된 불안은 아닌 것 같아요. 먹기 시작하면서 멈추지 못할까 봐 걱정하는 건 아니에요. 그보다는 먹기 전에 조심하는 편이고, 불편해지는 지경까지 안 가게 하려고 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 본인의 식습관이 먹는 양에 대한 통제력을 잃는 것에 대한 두려움에 의해 좌우된다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 정확히는 그렇지 않은 것 같아요. 먹기 시작하면 통제력을 잃을까 봐 두렵다는 느낌은 딱히 없어요. 그보다는 모든 걸 적당히 조절하려 하고, 불편해지지 않게 하려는 거예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 본인의 식습관이 특정 체중이나 몸매를 유지하는 것을 목표로 한다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네, 그런 것 같아요. 더 무거워지지 않으려고 해요. 피자나 큰 샌드위치 같은 걸 먹으면, 다음 날 더 커지고 느려질 것 같은 불안한 느낌이 들고, 그럼 사다리나 좁은 방을 필요한 만큼 돌아다닐 수 없을 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 지난 몇 달 동안 체중이 상당히 많이 줄으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 네, 그러니까... 작업복 바지가 예전보다 확실히 헐렁해요. 요즘은 그냥 헐렁하게 걸쳐 있어요. 현장 사람들이 너무 말랐다고 하는데, 저는 그냥 하루 종일 서서 일해서 살이 빠진 거라고 보는 편이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 체중이 늘 것에 대한 두려움이 직장 밖의 일상 활동이나 인간관계에 영향을 주나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 네, 어느 정도는요. 여전히 일이랑 수업은 나가고 있어서, 모든 걸 그만둔 건 아니에요. 근데 동료들이랑 점심을 먹거나 스터디 모임에 가는 건 피하기 시작했어요, 제 루틴을 지키고 사람들이 제가 뭘 먹는지 보거나 뭐라고 하는 걸 안 겪는 게 더 편하거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 본인이 너무 말랐다고 생각하시나요, 아니면 여전히 정상 체중이라고 보시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 다른 사람들처럼 무슨 응급 상황이라고는 딱히 안 보여요. 사람들이 저더러 너무 말랐다고 하는 건 아는데, 저한테는 그냥 절제하고 바쁘게 지내는 느낌이지, 제 체중에 심각하게 잘못된 게 있는 것 같지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 특정공포증 (D012) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 칼로리 섭취를 제한하려고 의식적으로 노력하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 네... 어떤 면에서는 그런 것 같아요. 제가 너무 적게 먹는다고 병원 선생님이 계속 말씀하셔서 여기 오게 됐어요. 대부분 날에는 그냥 간단하게 해요. 아침에 커피 마시고, 일하는 중간에 몇 입 먹고, 수업 과제에 너무 매여 있지 않으면 저녁을 조금 먹어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 특정공포증 (D012) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 먹는 것을 제한하는 주된 목표가 체중이 늘지 않게 하려는 건가요, 아니면 특정 몸매를 만들려는 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 대부분 체중이 늘지 않게 하려는 것 같아요. 그러니까, 피자나 큰 샌드위치처럼 무거운 걸 먹으면, 다음 날 더 커지고 느려질 것 같은 불안한 느낌이 들어요. 그리고 일할 때 필요한 만큼 사다리나 방을 돌아다닐 수 없을까 봐 걱정돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 특정공포증 (D012) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 피자나 큰 샌드위치 같은 무거운 식사를 피하는 목표가 주로 체중이 느는 게 두려워서인가요, 아니면 일을 위해 특정 몸매를 유지하고 싶어서인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 솔직히 체중이 느는 게 두려운 쪽에 더 가까워요. 일을 위한 특정 몸매를 딱히 생각하고 있는 건 아니에요. 무거운 걸 먹으면, 다음 날 더 커지고 무거워질까 봐 불안해지고, 그럼 사다리나 방을 필요한 만큼 돌아다닐 수 없을 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 특정공포증 (D012) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 다른 사람들이 너무 말랐다고 말할 때도, 본인이 너무 말랐다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 그러니까, 딱히 그렇지는 않아요. 사람들이 저더러 너무 말랐다고 하는 건 아는데, 그들처럼 무슨 응급 상황이라고는 안 봐요. 저한테는 그냥 별일 아닌 걸 크게 만드는 것처럼 느껴져요, 저는 그냥 절제하고 바쁜 것뿐인데요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 중간확률: 특정공포증 (D012) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 덜 먹는 목표가 특정 몸매를 만들기 위한 건가요, 아니면 그냥 체중이 늘지 않게 하려는 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 체중이 늘지 않게 하려는 쪽에 더 가까워요. 특정 몸매를 만들려는 건 아니에요. 그냥 피자나 큰 샌드위치처럼 무거운 걸 먹으면, 다음 날 더 커지고 느려질까 봐 정말 불안해지고, 그럼 일할 때 필요한 만큼 움직일 수 없을 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 토냐가 리드 페인터 자격증과 소규모 사업 계획을 위한 야간 강의를 듣기 시작하면서, 안 그래도 현장 업무와 견적, 수습생 멘토링으로 꽉 찼던 하루가 더 빡빡하고 시간에 쫓기게 되었다. 그녀는 긴 근무일 동안 효율적이고 저렴하며 통제 가능하다고 느껴지는 것을 중심으로 식사를 짜기 시작했고, 시간이 지나면서 이 절식은 그녀의 체중을 건강 수준보다 상당히 낮출 정도로 지속되었다. 고객과 동료들이 그녀가 눈에 띄게 마른 것을 알아챘는데도, 토냐는 이를 현장 체력과 깨끗한 생활 습관 덕분이라고 설명했고, 체중이 늘면 몸이 느려질 것 같다는 강한 두려움을 계속 느꼈으며, 자신의 저체중을 의학적으로 심각한 문제로 여기지 않았다. 자격증 서류를 검토하던 산업보건 임상의가 그녀의 저체중을 발견하고 섭식장애 평가를 의뢰하면서, 그녀는 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S043 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.
+  - S044 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.
+  - S045 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.
+  - S084 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신경성 식욕부진증 (D021, ICD: F50.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: anorexia_nervosa (관계=must_include, 요구개수=4, 충족개수=4, 커버리지=1.0)
-  확인된 근거: 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.; 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.; 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.; 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.
-  누락: 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.</t>
+          <t>의사의 최종 진단: 신경성 식욕부진증 (D021, ICD: F50.0)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: anorexia_nervosa (관계=must_include, 요구개수=4, 충족개수=4, 커버리지=1.0)
+확인된 근거:
+  - 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.
+  - 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.
+  - 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.
+  - 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D021_S003_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S003_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -985,6 +985,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1023,11 +1028,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D021_S003_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S003_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.65</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3553</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
